--- a/assets/constructions/examples/ctd_mhcb.xlsx
+++ b/assets/constructions/examples/ctd_mhcb.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN6"/>
+  <dimension ref="A1:AS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,11 +629,36 @@
           <t>dcsfms</t>
         </is>
       </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>49691000DL10 WP15PE</t>
+          <t>49691200DL12 WP15PE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -657,20 +682,20 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I2" t="n">
         <v>4</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>DUOLOCK:DL10</t>
+          <t>DUOLOCK:DL12</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -679,13 +704,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -711,20 +736,20 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="W2" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="X2" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
         <v>20</v>
       </c>
       <c r="AA2" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
@@ -752,7 +777,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>ZDL10</t>
+          <t>ZDL12</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -761,6 +786,17 @@
         </is>
       </c>
       <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>PMKSH</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -893,11 +929,22 @@
         </is>
       </c>
       <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>PMKSH</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>49691200DL12 WP15PE</t>
+          <t>49691600DL16 WP15PE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -921,20 +968,20 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I4" t="n">
         <v>4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>DUOLOCK:DL12</t>
+          <t>DUOLOCK:DL16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -943,13 +990,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="M4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -975,20 +1022,20 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="W4" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="X4" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
         <v>20</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.5</v>
+        <v>13</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -1016,7 +1063,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>ZDL12</t>
+          <t>ZDL16</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1025,11 +1072,22 @@
         </is>
       </c>
       <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>PMKSH</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>49691600DL16 WP15PE</t>
+          <t>49691000DL10 WP15PE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1053,20 +1111,20 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>DUOLOCK:DL16</t>
+          <t>DUOLOCK:DL10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1075,13 +1133,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="M5" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="N5" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1107,20 +1165,20 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="W5" t="n">
-        <v>15.5</v>
+        <v>9.6</v>
       </c>
       <c r="X5" t="n">
-        <v>15.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
         <v>20</v>
       </c>
       <c r="AA5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
@@ -1148,7 +1206,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>ZDL16</t>
+          <t>ZDL10</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1157,6 +1215,17 @@
         </is>
       </c>
       <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>PMKSH</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1289,6 +1358,17 @@
         </is>
       </c>
       <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>PMKSH</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
